--- a/manejo_reportes/SOL/SOLPEND.xlsx
+++ b/manejo_reportes/SOL/SOLPEND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\report_download\manejo_reportes\SOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFB07022-5593-4ECB-A43B-DFC8EAEC5E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67108F98-97F7-455F-A258-9C7AD7A4D0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" tabRatio="500"/>
   </bookViews>
@@ -1880,7 +1880,7 @@
         <xdr:cNvPr id="257" name="Picture -767">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8950F5E-026B-0B1C-B41B-626DFB38F6F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26126709-1ACD-82E2-DC38-FD0C772BB1AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="AA9" s="9"/>
       <c r="AC9" s="8">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="AD9" s="8"/>
     </row>
@@ -11877,14 +11877,14 @@
       <c r="W228" s="15"/>
       <c r="X228" s="15"/>
       <c r="Y228" s="16">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="Z228" s="16"/>
       <c r="AA228" s="16"/>
       <c r="AB228" s="16"/>
       <c r="AC228" s="16"/>
       <c r="AD228" s="17">
-        <v>0.3266087962962963</v>
+        <v>0.38280092592592591</v>
       </c>
       <c r="AE228" s="17"/>
       <c r="AF228" s="17"/>
